--- a/Thesis/H2S AEGL.xlsx
+++ b/Thesis/H2S AEGL.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gavin\Documents\GitHub\evac\Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2242963A-464A-455D-BC3B-847F6A76FACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91F0C28-DB12-435A-A317-AA3F75459C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
-    <sheet name="Φύλλο2" sheetId="4" r:id="rId1"/>
+    <sheet name="New_AEGL" sheetId="4" r:id="rId1"/>
+    <sheet name="ppm-dist" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
   <si>
     <t>Fit Smell</t>
   </si>
@@ -51,16 +52,238 @@
   </si>
   <si>
     <t>t(sec)</t>
+  </si>
+  <si>
+    <t>Distance</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>ppm</t>
+  </si>
+  <si>
+    <t>91.7</t>
+  </si>
+  <si>
+    <t>183.5</t>
+  </si>
+  <si>
+    <t>275.2</t>
+  </si>
+  <si>
+    <t>366.9</t>
+  </si>
+  <si>
+    <t>458.6</t>
+  </si>
+  <si>
+    <t>550.4</t>
+  </si>
+  <si>
+    <t>642.1</t>
+  </si>
+  <si>
+    <t>733.8</t>
+  </si>
+  <si>
+    <t>825.5</t>
+  </si>
+  <si>
+    <t>meters</t>
+  </si>
+  <si>
+    <t>pixels</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>#4F4F4F</t>
+  </si>
+  <si>
+    <t>#8F8F8F</t>
+  </si>
+  <si>
+    <t>#A8A8A8</t>
+  </si>
+  <si>
+    <t>#B8B8B8</t>
+  </si>
+  <si>
+    <t>#C2C2C2</t>
+  </si>
+  <si>
+    <t>#C7C7C7</t>
+  </si>
+  <si>
+    <t>#CCCCCC</t>
+  </si>
+  <si>
+    <t>#D1D1D1</t>
+  </si>
+  <si>
+    <t>#D4D4D4</t>
+  </si>
+  <si>
+    <t>#D6D6D6</t>
+  </si>
+  <si>
+    <t>Distance * 1000</t>
+  </si>
+  <si>
+    <t>1000 - ppm</t>
+  </si>
+  <si>
+    <t>(1000-ppm)/10</t>
+  </si>
+  <si>
+    <t>time (sec)</t>
+  </si>
+  <si>
+    <t>ppm*255/1000</t>
+  </si>
+  <si>
+    <t>afafaf</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>seconds</t>
+  </si>
+  <si>
+    <t>Assume only CH4</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Total leakage</t>
+  </si>
+  <si>
+    <t>kmol</t>
+  </si>
+  <si>
+    <t>0.77% H2S</t>
+  </si>
+  <si>
+    <t>mol H2S / s</t>
+  </si>
+  <si>
+    <t>kmol H2S / h</t>
+  </si>
+  <si>
+    <t>mol H2S / h</t>
+  </si>
+  <si>
+    <t>ppm H2S / s</t>
+  </si>
+  <si>
+    <t>CM1</t>
+  </si>
+  <si>
+    <t>CM2</t>
+  </si>
+  <si>
+    <t>CM3</t>
+  </si>
+  <si>
+    <t>CM4</t>
+  </si>
+  <si>
+    <t>CM5</t>
+  </si>
+  <si>
+    <t>CM6</t>
+  </si>
+  <si>
+    <t>CM7</t>
+  </si>
+  <si>
+    <t>CM8</t>
+  </si>
+  <si>
+    <t>ppm*255/1000 (2/3)</t>
+  </si>
+  <si>
+    <t>ppm (2/3)</t>
+  </si>
+  <si>
+    <t>hex</t>
+  </si>
+  <si>
+    <t>ppm (2/3) *255/1000</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>ppm (1/2)</t>
+  </si>
+  <si>
+    <t>ppm (1/2) *255/1000</t>
+  </si>
+  <si>
+    <t>ppm*255/1000 (1/2)</t>
+  </si>
+  <si>
+    <t>#585858</t>
+  </si>
+  <si>
+    <t>#383838</t>
+  </si>
+  <si>
+    <t>#2B2B2B</t>
+  </si>
+  <si>
+    <t>#282828</t>
+  </si>
+  <si>
+    <t>#242424</t>
+  </si>
+  <si>
+    <t>#1A1A1A</t>
+  </si>
+  <si>
+    <t>#151515</t>
+  </si>
+  <si>
+    <t>Meters to Pixels</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>c(t)=1800*t^(-0,227)</t>
+  </si>
+  <si>
+    <t>c(t)=850*t^(-0,227)</t>
+  </si>
+  <si>
+    <t>c(t)=600*t^(-0,227)</t>
+  </si>
+  <si>
+    <t>c(t)=8.5*t^(-0,227)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -74,7 +297,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -82,11 +305,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -96,6 +328,17 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -112,6 +355,1969 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Dist - ppm</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="el-GR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.9785651793525808E-3"/>
+                  <c:y val="0.12503171478565178"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="el-GR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ppm-dist'!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.07</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ppm-dist'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>281</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-20F2-4EFD-BEE2-8224BE699987}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="553751240"/>
+        <c:axId val="553748720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="553751240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553748720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="553748720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553751240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="el-GR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Time - Dist</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="el-GR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.10554351260028356"/>
+                  <c:y val="0.27064257886344584"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="el-GR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'ppm-dist'!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.07</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'ppm-dist'!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7950-41E8-BE57-5E50EEF7C59D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="530002688"/>
+        <c:axId val="530007008"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="530002688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="530007008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="530007008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="530002688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="el-GR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>464966</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>126316</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>348761</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>99646</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Γράφημα 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47EE1AE7-A9A9-16C0-EC7A-6E0E6982CA35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>126170</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>59202</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>391845</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>30920</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Γράφημα 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6647ADD-3016-22A5-12F4-889CA30D639A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,298 +2617,1423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A98D481-72B6-4B6F-8EF9-8F39EB86247A}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="14.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="2">
         <v>493.13517353857929</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>300</v>
       </c>
-      <c r="C2" s="1">
-        <f>B2/60</f>
+      <c r="D2" s="1">
+        <f>C2/60</f>
         <v>5</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>493.13517353857929</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>439.14335359378231</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>375.20835895751202</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>342.21558912436569</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>292.39233283217675</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2">
         <v>439.14335359378231</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="1">
         <v>500</v>
       </c>
-      <c r="C3" s="1">
-        <f t="shared" ref="C3:C6" si="0">B3/60</f>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D6" si="0">C3/60</f>
         <v>8.3333333333333339</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="2">
         <v>375.20835895751202</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C4" s="1">
         <v>1000</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <f t="shared" si="0"/>
         <v>16.666666666666668</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="2">
         <v>342.21558912436569</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="1">
         <v>1500</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="2">
         <v>292.39233283217675</v>
       </c>
-      <c r="B6" s="1">
+      <c r="C6" s="1">
         <v>3000</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="2">
         <v>232.86938750432913</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C10" s="1">
         <v>300</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>232.86938750432913</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>207.37325030817499</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>177.18172506326957</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>161.60180597539491</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>138.07415717075011</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="2">
         <v>207.37325030817499</v>
       </c>
-      <c r="B11" s="1">
+      <c r="C11" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="2">
         <v>177.18172506326957</v>
       </c>
-      <c r="B12" s="1">
+      <c r="C12" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="2">
         <v>161.60180597539491</v>
       </c>
-      <c r="B13" s="1">
+      <c r="C13" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="2">
         <v>138.07415717075011</v>
       </c>
-      <c r="B14" s="1">
+      <c r="C14" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="2">
         <v>164.37839117952643</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C18" s="1">
         <v>300</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>164.37839117952643</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>146.3811178645941</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>125.06945298583734</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>114.07186304145523</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>97.464110944058902</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="2">
         <v>146.3811178645941</v>
       </c>
-      <c r="B19" s="1">
+      <c r="C19" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="2">
         <v>125.06945298583734</v>
       </c>
-      <c r="B20" s="1">
+      <c r="C20" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="2">
         <v>114.07186304145523</v>
       </c>
-      <c r="B21" s="1">
+      <c r="C21" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="2">
         <v>97.464110944058902</v>
       </c>
-      <c r="B22" s="1">
+      <c r="C22" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="3">
         <v>2.3286938750432911</v>
       </c>
-      <c r="B26" s="1">
+      <c r="C26" s="1">
         <v>300</v>
       </c>
-      <c r="D26" s="3">
+      <c r="E26" s="3">
         <v>2.3286938750432911</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2.0737325030817497</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1.7718172506326957</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1.6160180597539491</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1.3807415717075011</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="3">
         <v>2.0737325030817497</v>
       </c>
-      <c r="B27" s="1">
+      <c r="C27" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="3">
         <v>1.7718172506326957</v>
       </c>
-      <c r="B28" s="1">
+      <c r="C28" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="7"/>
+      <c r="B29" s="3">
         <v>1.6160180597539491</v>
       </c>
-      <c r="B29" s="1">
+      <c r="C29" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="7"/>
+      <c r="B30" s="3">
         <v>1.3807415717075011</v>
       </c>
-      <c r="B30" s="1">
+      <c r="C30" s="1">
         <v>3000</v>
       </c>
     </row>
+    <row r="35" spans="1:3" s="8" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="2">
+        <f>1800*C37^(-0.227)</f>
+        <v>607.15330337425485</v>
+      </c>
+      <c r="C37" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="7"/>
+      <c r="B38" s="2">
+        <f t="shared" ref="B38:B41" si="1">1800*C38^(-0.227)</f>
+        <v>493.13517353857929</v>
+      </c>
+      <c r="C38" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="7"/>
+      <c r="B39" s="2">
+        <f t="shared" si="1"/>
+        <v>443.23162915052404</v>
+      </c>
+      <c r="C39" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="7"/>
+      <c r="B40" s="2">
+        <f t="shared" si="1"/>
+        <v>384.29032922710877</v>
+      </c>
+      <c r="C40" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="2">
+        <f t="shared" si="1"/>
+        <v>328.34140062136413</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="2">
+        <f>850*C45^(-0.227)</f>
+        <v>286.71128214895367</v>
+      </c>
+      <c r="C45" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="7"/>
+      <c r="B46" s="2">
+        <f t="shared" ref="B46:B49" si="2">850*C46^(-0.227)</f>
+        <v>232.86938750432913</v>
+      </c>
+      <c r="C46" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="7"/>
+      <c r="B47" s="2">
+        <f t="shared" si="2"/>
+        <v>209.30382487663636</v>
+      </c>
+      <c r="C47" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="7"/>
+      <c r="B48" s="2">
+        <f t="shared" si="2"/>
+        <v>181.47043324613469</v>
+      </c>
+      <c r="C48" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="7"/>
+      <c r="B49" s="2">
+        <f t="shared" si="2"/>
+        <v>155.05010584897749</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="2">
+        <f>600*C53^(-0.227)</f>
+        <v>202.38443445808497</v>
+      </c>
+      <c r="C53" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="7"/>
+      <c r="B54" s="2">
+        <f t="shared" ref="B54:B57" si="3">600*C54^(-0.227)</f>
+        <v>164.37839117952643</v>
+      </c>
+      <c r="C54" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="7"/>
+      <c r="B55" s="2">
+        <f t="shared" si="3"/>
+        <v>147.74387638350802</v>
+      </c>
+      <c r="C55" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="7"/>
+      <c r="B56" s="2">
+        <f t="shared" si="3"/>
+        <v>128.09677640903624</v>
+      </c>
+      <c r="C56" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="7"/>
+      <c r="B57" s="2">
+        <f t="shared" si="3"/>
+        <v>109.44713354045471</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="2">
+        <f>8.5*C61^(-0.227)</f>
+        <v>2.8671128214895369</v>
+      </c>
+      <c r="C61" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="7"/>
+      <c r="B62" s="2">
+        <f t="shared" ref="B62:B65" si="4">8.5*C62^(-0.227)</f>
+        <v>2.3286938750432911</v>
+      </c>
+      <c r="C62" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="7"/>
+      <c r="B63" s="2">
+        <f t="shared" si="4"/>
+        <v>2.0930382487663635</v>
+      </c>
+      <c r="C63" s="1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="7"/>
+      <c r="B64" s="2">
+        <f t="shared" si="4"/>
+        <v>1.8147043324613468</v>
+      </c>
+      <c r="C64" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="7"/>
+      <c r="B65" s="2">
+        <f t="shared" si="4"/>
+        <v>1.5505010584897752</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1800</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="A45:A49"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D976B459-1B7D-4296-8012-F11251EFF08E}">
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>317</v>
+      </c>
+      <c r="B2">
+        <v>1.07</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <f>B2*723.37/2500*1000</f>
+        <v>309.60236000000003</v>
+      </c>
+      <c r="E2" s="6">
+        <f>A2*2/3</f>
+        <v>211.33333333333334</v>
+      </c>
+      <c r="F2" s="5">
+        <f>E2*255/1000</f>
+        <v>53.89</v>
+      </c>
+      <c r="I2" s="5">
+        <f>A2/2</f>
+        <v>158.5</v>
+      </c>
+      <c r="J2" s="5">
+        <f>I2*255/1000</f>
+        <v>40.417499999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>281</v>
+      </c>
+      <c r="B3">
+        <v>1.27</v>
+      </c>
+      <c r="C3">
+        <v>120</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D5" si="0">B3*723.37/2500*1000</f>
+        <v>367.47195999999997</v>
+      </c>
+      <c r="E3" s="6">
+        <f t="shared" ref="E3:E5" si="1">A3*2/3</f>
+        <v>187.33333333333334</v>
+      </c>
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F5" si="2">E3*255/1000</f>
+        <v>47.77</v>
+      </c>
+      <c r="I3" s="5">
+        <f t="shared" ref="I3:I5" si="3">A3/2</f>
+        <v>140.5</v>
+      </c>
+      <c r="J3" s="5">
+        <f t="shared" ref="J3:J5" si="4">I3*255/1000</f>
+        <v>35.827500000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>200</v>
+      </c>
+      <c r="B4">
+        <v>2.13</v>
+      </c>
+      <c r="C4">
+        <v>215</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>616.31124</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" si="1"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="4"/>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>164</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>300</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>868.04399999999998</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="1"/>
+        <v>109.33333333333333</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="2"/>
+        <v>27.88</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" si="3"/>
+        <v>82</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" si="4"/>
+        <v>20.91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>0.317</v>
+      </c>
+      <c r="B9" s="4">
+        <f>328.71*A9^(-0.641)</f>
+        <v>686.48954787651837</v>
+      </c>
+      <c r="C9">
+        <v>9.3718832874999976</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="5">
+        <v>175.05483470851217</v>
+      </c>
+      <c r="F9">
+        <v>317</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" ref="G9:G18" si="5">1000-B9</f>
+        <v>313.51045212348163</v>
+      </c>
+      <c r="H9" s="5">
+        <f>G9/10</f>
+        <v>31.351045212348161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="B10" s="4">
+        <f t="shared" ref="B10:B18" si="6">328.71*A10^(-0.641)</f>
+        <v>440.22398628267081</v>
+      </c>
+      <c r="C10">
+        <v>47.789973149999994</v>
+      </c>
+      <c r="D10">
+        <v>707070</v>
+      </c>
+      <c r="E10" s="5">
+        <v>112.25711650208106</v>
+      </c>
+      <c r="F10">
+        <v>634</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="5"/>
+        <v>559.77601371732919</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" ref="H10:H18" si="7">G10/10</f>
+        <v>55.977601371732916</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="B11" s="4">
+        <f t="shared" si="6"/>
+        <v>339.46828397332285</v>
+      </c>
+      <c r="C11">
+        <v>85.12026958749999</v>
+      </c>
+      <c r="D11">
+        <v>575757</v>
+      </c>
+      <c r="E11" s="5">
+        <v>86.564412413197317</v>
+      </c>
+      <c r="F11">
+        <v>951</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="5"/>
+        <v>660.53171602667715</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="7"/>
+        <v>66.053171602667717</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>1.268</v>
+      </c>
+      <c r="B12" s="4">
+        <f t="shared" si="6"/>
+        <v>282.30168791071554</v>
+      </c>
+      <c r="C12">
+        <v>121.36277259999999</v>
+      </c>
+      <c r="E12" s="5">
+        <v>71.986930417232458</v>
+      </c>
+      <c r="F12">
+        <v>1268</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="5"/>
+        <v>717.6983120892844</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="7"/>
+        <v>71.769831208928437</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>1.585</v>
+      </c>
+      <c r="B13" s="4">
+        <f t="shared" si="6"/>
+        <v>244.67756877690817</v>
+      </c>
+      <c r="C13">
+        <v>156.51748218749998</v>
+      </c>
+      <c r="E13" s="5">
+        <v>62.392780038111582</v>
+      </c>
+      <c r="F13">
+        <v>1585</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="5"/>
+        <v>755.32243122309183</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="7"/>
+        <v>75.532243122309183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>1.9019999999999999</v>
+      </c>
+      <c r="B14" s="4">
+        <f t="shared" si="6"/>
+        <v>217.69024983633781</v>
+      </c>
+      <c r="C14">
+        <v>190.58439835000001</v>
+      </c>
+      <c r="E14" s="5">
+        <v>55.511013708266148</v>
+      </c>
+      <c r="F14">
+        <v>1902</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="5"/>
+        <v>782.30975016366222</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="7"/>
+        <v>78.230975016366216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>2.2189999999999999</v>
+      </c>
+      <c r="B15" s="4">
+        <f>328.71*A15^(-0.641)</f>
+        <v>197.20870699513659</v>
+      </c>
+      <c r="C15">
+        <v>223.56352108749996</v>
+      </c>
+      <c r="E15" s="5">
+        <v>50.288220283759827</v>
+      </c>
+      <c r="F15">
+        <v>2219</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" si="5"/>
+        <v>802.79129300486341</v>
+      </c>
+      <c r="H15" s="5">
+        <f t="shared" si="7"/>
+        <v>80.279129300486346</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>2.536</v>
+      </c>
+      <c r="B16" s="4">
+        <f t="shared" si="6"/>
+        <v>181.03112388352878</v>
+      </c>
+      <c r="C16">
+        <v>255.45485039999994</v>
+      </c>
+      <c r="E16" s="5">
+        <v>46.162936590299843</v>
+      </c>
+      <c r="F16">
+        <v>2536</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="5"/>
+        <v>818.96887611647117</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="7"/>
+        <v>81.896887611647117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>2.8530000000000002</v>
+      </c>
+      <c r="B17" s="4">
+        <f t="shared" si="6"/>
+        <v>167.86667208591064</v>
+      </c>
+      <c r="C17">
+        <v>286.2583862875</v>
+      </c>
+      <c r="E17" s="5">
+        <v>42.806001381907215</v>
+      </c>
+      <c r="F17">
+        <v>2853</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="5"/>
+        <v>832.13332791408936</v>
+      </c>
+      <c r="H17" s="5">
+        <f t="shared" si="7"/>
+        <v>83.213332791408931</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>3.17</v>
+      </c>
+      <c r="B18" s="4">
+        <f t="shared" si="6"/>
+        <v>156.90396891563105</v>
+      </c>
+      <c r="C18">
+        <v>315.97412874999998</v>
+      </c>
+      <c r="E18" s="5">
+        <v>40.010512073485913</v>
+      </c>
+      <c r="F18">
+        <v>3170</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="5"/>
+        <v>843.09603108436897</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="7"/>
+        <v>84.309603108436903</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>317</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="5">
+        <f>2/3*E9</f>
+        <v>116.70322313900812</v>
+      </c>
+      <c r="F24" s="5">
+        <f>E9/2</f>
+        <v>87.527417354256087</v>
+      </c>
+      <c r="G24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>634</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" ref="E25:E33" si="8">2/3*E10</f>
+        <v>74.838077668054041</v>
+      </c>
+      <c r="F25" s="5">
+        <f t="shared" ref="F25:F33" si="9">E10/2</f>
+        <v>56.128558251040531</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="5">
+        <v>87.527417354256087</v>
+      </c>
+      <c r="I25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>951</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="8"/>
+        <v>57.709608275464873</v>
+      </c>
+      <c r="F26" s="5">
+        <f t="shared" si="9"/>
+        <v>43.282206206598659</v>
+      </c>
+      <c r="G26" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="5">
+        <v>56.128558251040531</v>
+      </c>
+      <c r="I26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>1268</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="8"/>
+        <v>47.991286944821638</v>
+      </c>
+      <c r="F27" s="5">
+        <f t="shared" si="9"/>
+        <v>35.993465208616229</v>
+      </c>
+      <c r="G27" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="5">
+        <v>43.282206206598659</v>
+      </c>
+      <c r="I27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>1585</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="5">
+        <f t="shared" si="8"/>
+        <v>41.595186692074385</v>
+      </c>
+      <c r="F28" s="5">
+        <f t="shared" si="9"/>
+        <v>31.196390019055791</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="5">
+        <v>40.417499999999997</v>
+      </c>
+      <c r="I28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1902</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="5">
+        <f t="shared" si="8"/>
+        <v>37.007342472177427</v>
+      </c>
+      <c r="F29" s="5">
+        <f t="shared" si="9"/>
+        <v>27.755506854133074</v>
+      </c>
+      <c r="G29" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="5">
+        <v>35.827500000000001</v>
+      </c>
+      <c r="I29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>2219</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="5">
+        <f t="shared" si="8"/>
+        <v>33.525480189173216</v>
+      </c>
+      <c r="F30" s="5">
+        <f t="shared" si="9"/>
+        <v>25.144110141879914</v>
+      </c>
+      <c r="G30" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30" s="5">
+        <v>25.5</v>
+      </c>
+      <c r="I30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>2536</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="5">
+        <f t="shared" si="8"/>
+        <v>30.775291060199894</v>
+      </c>
+      <c r="F31" s="5">
+        <f t="shared" si="9"/>
+        <v>23.081468295149921</v>
+      </c>
+      <c r="G31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="5">
+        <v>20.91</v>
+      </c>
+      <c r="I31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>2853</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="5">
+        <f t="shared" si="8"/>
+        <v>28.537334254604808</v>
+      </c>
+      <c r="F32" s="5">
+        <f t="shared" si="9"/>
+        <v>21.403000690953608</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>3170</v>
+      </c>
+      <c r="B33" s="5">
+        <v>843.09603108436897</v>
+      </c>
+      <c r="C33" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="5">
+        <f t="shared" si="8"/>
+        <v>26.673674715657274</v>
+      </c>
+      <c r="F33" s="5">
+        <f t="shared" si="9"/>
+        <v>20.005256036742956</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>3600</v>
+      </c>
+      <c r="C37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38">
+        <v>263</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="4">
+        <v>16.4375</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="4">
+        <v>0.12656875000000001</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="4">
+        <v>126.56875000000001</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="4">
+        <v>3.5157986111111116E-2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="4">
+        <v>35157.986111111117</v>
+      </c>
+      <c r="C43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Thesis/H2S AEGL.xlsx
+++ b/Thesis/H2S AEGL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gavin\Documents\GitHub\evac\Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91F0C28-DB12-435A-A317-AA3F75459C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FFB0C2-A759-4219-869C-C6E1BC23B2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="New_AEGL" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
   <si>
     <t>Fit Smell</t>
   </si>
@@ -144,9 +144,6 @@
     <t>ppm*255/1000</t>
   </si>
   <si>
-    <t>afafaf</t>
-  </si>
-  <si>
     <t>Duration</t>
   </si>
   <si>
@@ -268,6 +265,18 @@
   </si>
   <si>
     <t>c(t)=8.5*t^(-0,227)</t>
+  </si>
+  <si>
+    <t>AFAFAF</t>
+  </si>
+  <si>
+    <t>3F3F3F</t>
+  </si>
+  <si>
+    <t>2E2E2E</t>
+  </si>
+  <si>
+    <t>2B2B2B</t>
   </si>
 </sst>
 </file>
@@ -334,11 +343,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2627,7 +2636,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -2637,8 +2646,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>73</v>
+      <c r="A2" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="B2" s="2">
         <v>493.13517353857929</v>
@@ -2667,7 +2676,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
+      <c r="A3" s="8"/>
       <c r="B3" s="2">
         <v>439.14335359378231</v>
       </c>
@@ -2680,7 +2689,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="2">
         <v>375.20835895751202</v>
       </c>
@@ -2693,7 +2702,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="2">
         <v>342.21558912436569</v>
       </c>
@@ -2706,7 +2715,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="2">
         <v>292.39233283217675</v>
       </c>
@@ -2733,8 +2742,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>74</v>
+      <c r="A10" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="B10" s="2">
         <v>232.86938750432913</v>
@@ -2759,7 +2768,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
+      <c r="A11" s="8"/>
       <c r="B11" s="2">
         <v>207.37325030817499</v>
       </c>
@@ -2768,7 +2777,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="2">
         <v>177.18172506326957</v>
       </c>
@@ -2777,7 +2786,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="2">
         <v>161.60180597539491</v>
       </c>
@@ -2786,7 +2795,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
+      <c r="A14" s="8"/>
       <c r="B14" s="2">
         <v>138.07415717075011</v>
       </c>
@@ -2809,8 +2818,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>75</v>
+      <c r="A18" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="B18" s="2">
         <v>164.37839117952643</v>
@@ -2835,7 +2844,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="2">
         <v>146.3811178645941</v>
       </c>
@@ -2844,7 +2853,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
+      <c r="A20" s="8"/>
       <c r="B20" s="2">
         <v>125.06945298583734</v>
       </c>
@@ -2853,7 +2862,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
+      <c r="A21" s="8"/>
       <c r="B21" s="2">
         <v>114.07186304145523</v>
       </c>
@@ -2862,7 +2871,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
+      <c r="A22" s="8"/>
       <c r="B22" s="2">
         <v>97.464110944058902</v>
       </c>
@@ -2879,8 +2888,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>76</v>
+      <c r="A26" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B26" s="3">
         <v>2.3286938750432911</v>
@@ -2905,7 +2914,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
+      <c r="A27" s="8"/>
       <c r="B27" s="3">
         <v>2.0737325030817497</v>
       </c>
@@ -2914,7 +2923,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
+      <c r="A28" s="8"/>
       <c r="B28" s="3">
         <v>1.7718172506326957</v>
       </c>
@@ -2923,7 +2932,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
+      <c r="A29" s="8"/>
       <c r="B29" s="3">
         <v>1.6160180597539491</v>
       </c>
@@ -2932,7 +2941,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
+      <c r="A30" s="8"/>
       <c r="B30" s="3">
         <v>1.3807415717075011</v>
       </c>
@@ -2940,10 +2949,10 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="8" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:3" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>3</v>
@@ -2953,8 +2962,8 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>73</v>
+      <c r="A37" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="B37" s="2">
         <f>1800*C37^(-0.227)</f>
@@ -2965,7 +2974,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
+      <c r="A38" s="8"/>
       <c r="B38" s="2">
         <f t="shared" ref="B38:B41" si="1">1800*C38^(-0.227)</f>
         <v>493.13517353857929</v>
@@ -2975,7 +2984,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
+      <c r="A39" s="8"/>
       <c r="B39" s="2">
         <f t="shared" si="1"/>
         <v>443.23162915052404</v>
@@ -2985,7 +2994,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
+      <c r="A40" s="8"/>
       <c r="B40" s="2">
         <f t="shared" si="1"/>
         <v>384.29032922710877</v>
@@ -2995,7 +3004,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="7"/>
+      <c r="A41" s="8"/>
       <c r="B41" s="2">
         <f t="shared" si="1"/>
         <v>328.34140062136413</v>
@@ -3019,8 +3028,8 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>74</v>
+      <c r="A45" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="B45" s="2">
         <f>850*C45^(-0.227)</f>
@@ -3031,7 +3040,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="7"/>
+      <c r="A46" s="8"/>
       <c r="B46" s="2">
         <f t="shared" ref="B46:B49" si="2">850*C46^(-0.227)</f>
         <v>232.86938750432913</v>
@@ -3041,7 +3050,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="7"/>
+      <c r="A47" s="8"/>
       <c r="B47" s="2">
         <f t="shared" si="2"/>
         <v>209.30382487663636</v>
@@ -3051,7 +3060,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
+      <c r="A48" s="8"/>
       <c r="B48" s="2">
         <f t="shared" si="2"/>
         <v>181.47043324613469</v>
@@ -3061,7 +3070,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="7"/>
+      <c r="A49" s="8"/>
       <c r="B49" s="2">
         <f t="shared" si="2"/>
         <v>155.05010584897749</v>
@@ -3085,8 +3094,8 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>75</v>
+      <c r="A53" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="B53" s="2">
         <f>600*C53^(-0.227)</f>
@@ -3097,7 +3106,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="7"/>
+      <c r="A54" s="8"/>
       <c r="B54" s="2">
         <f t="shared" ref="B54:B57" si="3">600*C54^(-0.227)</f>
         <v>164.37839117952643</v>
@@ -3107,7 +3116,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="7"/>
+      <c r="A55" s="8"/>
       <c r="B55" s="2">
         <f t="shared" si="3"/>
         <v>147.74387638350802</v>
@@ -3117,7 +3126,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="7"/>
+      <c r="A56" s="8"/>
       <c r="B56" s="2">
         <f t="shared" si="3"/>
         <v>128.09677640903624</v>
@@ -3127,7 +3136,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="7"/>
+      <c r="A57" s="8"/>
       <c r="B57" s="2">
         <f t="shared" si="3"/>
         <v>109.44713354045471</v>
@@ -3145,8 +3154,8 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="s">
-        <v>76</v>
+      <c r="A61" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B61" s="2">
         <f>8.5*C61^(-0.227)</f>
@@ -3157,7 +3166,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="7"/>
+      <c r="A62" s="8"/>
       <c r="B62" s="2">
         <f t="shared" ref="B62:B65" si="4">8.5*C62^(-0.227)</f>
         <v>2.3286938750432911</v>
@@ -3167,7 +3176,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="7"/>
+      <c r="A63" s="8"/>
       <c r="B63" s="2">
         <f t="shared" si="4"/>
         <v>2.0930382487663635</v>
@@ -3177,7 +3186,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="7"/>
+      <c r="A64" s="8"/>
       <c r="B64" s="2">
         <f t="shared" si="4"/>
         <v>1.8147043324613468</v>
@@ -3187,7 +3196,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="7"/>
+      <c r="A65" s="8"/>
       <c r="B65" s="2">
         <f t="shared" si="4"/>
         <v>1.5505010584897752</v>
@@ -3213,10 +3222,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D976B459-1B7D-4296-8012-F11251EFF08E}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.09765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
@@ -3235,22 +3245,22 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" t="s">
-        <v>58</v>
-      </c>
       <c r="I1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" t="s">
         <v>61</v>
-      </c>
-      <c r="J1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3387,6 +3397,9 @@
       <c r="C8" t="s">
         <v>33</v>
       </c>
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
       <c r="E8" t="s">
         <v>34</v>
       </c>
@@ -3404,15 +3417,15 @@
       <c r="A9" s="4">
         <v>0.317</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <f>328.71*A9^(-0.641)</f>
         <v>686.48954787651837</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>9.3718832874999976</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="E9" s="5">
         <v>175.05483470851217</v>
@@ -3433,11 +3446,11 @@
       <c r="A10" s="4">
         <v>0.63400000000000001</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <f t="shared" ref="B10:B18" si="6">328.71*A10^(-0.641)</f>
         <v>440.22398628267081</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="5">
         <v>47.789973149999994</v>
       </c>
       <c r="D10">
@@ -3462,11 +3475,11 @@
       <c r="A11" s="4">
         <v>0.95099999999999996</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <f t="shared" si="6"/>
         <v>339.46828397332285</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="5">
         <v>85.12026958749999</v>
       </c>
       <c r="D11">
@@ -3491,12 +3504,15 @@
       <c r="A12" s="4">
         <v>1.268</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <f t="shared" si="6"/>
         <v>282.30168791071554</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="5">
         <v>121.36277259999999</v>
+      </c>
+      <c r="D12">
+        <v>484848</v>
       </c>
       <c r="E12" s="5">
         <v>71.986930417232458</v>
@@ -3517,12 +3533,15 @@
       <c r="A13" s="4">
         <v>1.585</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <f t="shared" si="6"/>
         <v>244.67756877690817</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="5">
         <v>156.51748218749998</v>
+      </c>
+      <c r="D13" t="s">
+        <v>77</v>
       </c>
       <c r="E13" s="5">
         <v>62.392780038111582</v>
@@ -3543,12 +3562,15 @@
       <c r="A14" s="4">
         <v>1.9019999999999999</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <f t="shared" si="6"/>
         <v>217.69024983633781</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="5">
         <v>190.58439835000001</v>
+      </c>
+      <c r="D14">
+        <v>383838</v>
       </c>
       <c r="E14" s="5">
         <v>55.511013708266148</v>
@@ -3569,12 +3591,15 @@
       <c r="A15" s="4">
         <v>2.2189999999999999</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <f>328.71*A15^(-0.641)</f>
         <v>197.20870699513659</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="5">
         <v>223.56352108749996</v>
+      </c>
+      <c r="D15">
+        <v>323232</v>
       </c>
       <c r="E15" s="5">
         <v>50.288220283759827</v>
@@ -3595,12 +3620,15 @@
       <c r="A16" s="4">
         <v>2.536</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <f t="shared" si="6"/>
         <v>181.03112388352878</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="5">
         <v>255.45485039999994</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
       </c>
       <c r="E16" s="5">
         <v>46.162936590299843</v>
@@ -3621,12 +3649,15 @@
       <c r="A17" s="4">
         <v>2.8530000000000002</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <f t="shared" si="6"/>
         <v>167.86667208591064</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="5">
         <v>286.2583862875</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
       </c>
       <c r="E17" s="5">
         <v>42.806001381907215</v>
@@ -3647,12 +3678,15 @@
       <c r="A18">
         <v>3.17</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <f t="shared" si="6"/>
         <v>156.90396891563105</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="5">
         <v>315.97412874999998</v>
+      </c>
+      <c r="D18">
+        <v>282828</v>
       </c>
       <c r="E18" s="5">
         <v>40.010512073485913</v>
@@ -3680,19 +3714,19 @@
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H23" t="s">
         <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -3714,7 +3748,7 @@
         <v>87.527417354256087</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3739,13 +3773,13 @@
         <v>56.128558251040531</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H25" s="5">
         <v>87.527417354256087</v>
       </c>
       <c r="I25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -3767,13 +3801,13 @@
         <v>43.282206206598659</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H26" s="5">
         <v>56.128558251040531</v>
       </c>
       <c r="I26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -3795,13 +3829,13 @@
         <v>35.993465208616229</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27" s="5">
         <v>43.282206206598659</v>
       </c>
       <c r="I27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -3823,13 +3857,13 @@
         <v>31.196390019055791</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H28" s="5">
         <v>40.417499999999997</v>
       </c>
       <c r="I28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -3851,13 +3885,13 @@
         <v>27.755506854133074</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29" s="5">
         <v>35.827500000000001</v>
       </c>
       <c r="I29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -3879,13 +3913,13 @@
         <v>25.144110141879914</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H30" s="5">
         <v>25.5</v>
       </c>
       <c r="I30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -3907,13 +3941,13 @@
         <v>23.081468295149921</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H31" s="5">
         <v>20.91</v>
       </c>
       <c r="I31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -3956,13 +3990,17 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="E36">
+        <f>A9*1000</f>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -3970,40 +4008,56 @@
         <v>3600</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="E37">
+        <f t="shared" ref="E37:E45" si="10">A10*1000</f>
+        <v>634</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>263</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="10"/>
+        <v>951</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="4">
         <v>16.4375</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="10"/>
+        <v>1268</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="4">
         <v>0.12656875000000001</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="10"/>
+        <v>1585</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -4011,7 +4065,11 @@
         <v>126.56875000000001</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="10"/>
+        <v>1902</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -4019,7 +4077,11 @@
         <v>3.5157986111111116E-2</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="10"/>
+        <v>2219</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -4027,7 +4089,23 @@
         <v>35157.986111111117</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="10"/>
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E44">
+        <f t="shared" si="10"/>
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E45">
+        <f t="shared" si="10"/>
+        <v>3170</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis/H2S AEGL.xlsx
+++ b/Thesis/H2S AEGL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gavin\Documents\GitHub\evac\Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FFB0C2-A759-4219-869C-C6E1BC23B2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B57C538-1338-46CA-BCFA-8DD7C7E3C1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="New_AEGL" sheetId="4" r:id="rId1"/>
@@ -283,6 +283,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -327,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -348,6 +351,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2949,8 +2955,8 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" s="7" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -2961,7 +2967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>72</v>
       </c>
@@ -2972,8 +2978,26 @@
       <c r="C37" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" s="1">
+        <v>607.15330337425485</v>
+      </c>
+      <c r="F37" s="9">
+        <v>607.15330337425485</v>
+      </c>
+      <c r="G37" s="9">
+        <v>493.13517353857929</v>
+      </c>
+      <c r="H37" s="9">
+        <v>443.23162915052404</v>
+      </c>
+      <c r="I37" s="9">
+        <v>384.29032922710877</v>
+      </c>
+      <c r="J37" s="9">
+        <v>328.34140062136413</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="2">
         <f t="shared" ref="B38:B41" si="1">1800*C38^(-0.227)</f>
@@ -2982,8 +3006,11 @@
       <c r="C38" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" s="1">
+        <v>493.13517353857929</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="2">
         <f t="shared" si="1"/>
@@ -2992,8 +3019,11 @@
       <c r="C39" s="1">
         <v>480</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" s="1">
+        <v>443.23162915052404</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="2">
         <f t="shared" si="1"/>
@@ -3002,8 +3032,11 @@
       <c r="C40" s="1">
         <v>900</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" s="1">
+        <v>384.29032922710877</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="2">
         <f t="shared" si="1"/>
@@ -3012,14 +3045,17 @@
       <c r="C41" s="1">
         <v>1800</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" s="1">
+        <v>328.34140062136413</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
         <v>2</v>
       </c>
@@ -3027,7 +3063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>73</v>
       </c>
@@ -3038,8 +3074,26 @@
       <c r="C45" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" s="1">
+        <v>286.71128214895367</v>
+      </c>
+      <c r="F45" s="9">
+        <v>286.71128214895367</v>
+      </c>
+      <c r="G45" s="9">
+        <v>232.86938750432913</v>
+      </c>
+      <c r="H45" s="9">
+        <v>209.30382487663636</v>
+      </c>
+      <c r="I45" s="9">
+        <v>181.47043324613469</v>
+      </c>
+      <c r="J45" s="9">
+        <v>155.05010584897749</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="2">
         <f t="shared" ref="B46:B49" si="2">850*C46^(-0.227)</f>
@@ -3048,8 +3102,11 @@
       <c r="C46" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" s="1">
+        <v>232.86938750432913</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="2">
         <f t="shared" si="2"/>
@@ -3058,8 +3115,11 @@
       <c r="C47" s="1">
         <v>480</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" s="1">
+        <v>209.30382487663636</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="2">
         <f t="shared" si="2"/>
@@ -3068,8 +3128,11 @@
       <c r="C48" s="1">
         <v>900</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" s="1">
+        <v>181.47043324613469</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="2">
         <f t="shared" si="2"/>
@@ -3078,14 +3141,17 @@
       <c r="C49" s="1">
         <v>1800</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="1">
+        <v>155.05010584897749</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
         <v>1</v>
       </c>
@@ -3093,7 +3159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>74</v>
       </c>
@@ -3104,8 +3170,26 @@
       <c r="C53" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" s="1">
+        <v>202.38443445808497</v>
+      </c>
+      <c r="F53" s="9">
+        <v>202.38443445808497</v>
+      </c>
+      <c r="G53" s="9">
+        <v>164.37839117952643</v>
+      </c>
+      <c r="H53" s="9">
+        <v>147.74387638350802</v>
+      </c>
+      <c r="I53" s="9">
+        <v>128.09677640903624</v>
+      </c>
+      <c r="J53" s="9">
+        <v>109.44713354045471</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="2">
         <f t="shared" ref="B54:B57" si="3">600*C54^(-0.227)</f>
@@ -3114,8 +3198,11 @@
       <c r="C54" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" s="1">
+        <v>164.37839117952643</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="2">
         <f t="shared" si="3"/>
@@ -3124,8 +3211,11 @@
       <c r="C55" s="1">
         <v>480</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" s="1">
+        <v>147.74387638350802</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="2">
         <f t="shared" si="3"/>
@@ -3134,8 +3224,11 @@
       <c r="C56" s="1">
         <v>900</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" s="1">
+        <v>128.09677640903624</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="2">
         <f t="shared" si="3"/>
@@ -3144,8 +3237,11 @@
       <c r="C57" s="1">
         <v>1800</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" s="1">
+        <v>109.44713354045471</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
         <v>0</v>
       </c>
@@ -3153,7 +3249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>75</v>
       </c>
@@ -3164,8 +3260,26 @@
       <c r="C61" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61" s="9">
+        <v>2.8671128214895369</v>
+      </c>
+      <c r="F61" s="9">
+        <v>2.8671128214895369</v>
+      </c>
+      <c r="G61" s="9">
+        <v>2.3286938750432911</v>
+      </c>
+      <c r="H61" s="9">
+        <v>2.0930382487663635</v>
+      </c>
+      <c r="I61" s="9">
+        <v>1.8147043324613468</v>
+      </c>
+      <c r="J61" s="9">
+        <v>1.5505010584897752</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="2">
         <f t="shared" ref="B62:B65" si="4">8.5*C62^(-0.227)</f>
@@ -3174,8 +3288,11 @@
       <c r="C62" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62" s="9">
+        <v>2.3286938750432911</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="2">
         <f t="shared" si="4"/>
@@ -3184,8 +3301,11 @@
       <c r="C63" s="1">
         <v>480</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" s="9">
+        <v>2.0930382487663635</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="2">
         <f t="shared" si="4"/>
@@ -3194,8 +3314,11 @@
       <c r="C64" s="1">
         <v>900</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64" s="9">
+        <v>1.8147043324613468</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="2">
         <f t="shared" si="4"/>
@@ -3203,6 +3326,9 @@
       </c>
       <c r="C65" s="1">
         <v>1800</v>
+      </c>
+      <c r="D65" s="9">
+        <v>1.5505010584897752</v>
       </c>
     </row>
   </sheetData>
